--- a/scripts/checks/results/HLR_results_10_All_lg_families_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_10_All_lg_families_noLgArea_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E2" t="n">
-        <v>1544</v>
+        <v>1877</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2788887100714704</v>
+        <v>0.2274601493467305</v>
       </c>
       <c r="H2" t="n">
-        <v>597.139684767698</v>
+        <v>552.6481254821807</v>
       </c>
       <c r="I2" t="n">
-        <v>9.159653958517076e-112</v>
+        <v>2.509992414891764e-107</v>
       </c>
       <c r="J2" t="n">
-        <v>172.1361681705525</v>
+        <v>210.6653267677102</v>
       </c>
       <c r="K2" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L2" t="n">
-        <v>66.5734049212974</v>
+        <v>62.02653060323181</v>
       </c>
       <c r="M2" t="n">
-        <v>0.111487155550876</v>
+        <v>0.1122351234777358</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7216232857673603, 'N1ratio-ArgsPreds': -0.20623521687888982}</t>
+          <t>{'const': 0.5696950682749405, 'N1ratio-ArgsPreds': -2.2180953249680244}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 5.823844912460471e-164, 'N1ratio-ArgsPreds': 9.159653958519536e-112}</t>
+          <t>{'const': 8.066049526466469e-170, 'N1ratio-ArgsPreds': 2.5099924148907162e-107}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5280991479556377}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4769278240433563}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5280991479556364)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5280991479556364)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.888871007146914)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.746014934673116)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E3" t="n">
-        <v>1543</v>
+        <v>1876</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2789071308413007</v>
+        <v>0.2274861049803184</v>
       </c>
       <c r="H3" t="n">
-        <v>298.4037987993292</v>
+        <v>276.2176419701839</v>
       </c>
       <c r="I3" t="n">
-        <v>2.755570156435227e-110</v>
+        <v>7.179746887012252e-106</v>
       </c>
       <c r="J3" t="n">
-        <v>172.1317709564503</v>
+        <v>210.6582488777779</v>
       </c>
       <c r="K3" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L3" t="n">
-        <v>33.28890106769981</v>
+        <v>31.01680424658205</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1115565592718408</v>
+        <v>0.1122911774401801</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7201931552183973, 'N1ratio-ArgsPreds': -0.2065815817472107, 'Fam_class': 4.7708430958967444e-05}</t>
+          <t>{'const': 0.5714134856817259, 'N1ratio-ArgsPreds': -2.212979453130236, 'Fam_class': -4.804542163441746e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 5.137391410263117e-152, 'N1ratio-ArgsPreds': 3.811566591989392e-108, 'Fam_class': 0.8426511669010686}</t>
+          <t>{'const': 1.6803457582878222e-153, 'N1ratio-ArgsPreds': 1.0515195149464727e-102, 'Fam_class': 0.8017945188393122}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5289860720930872, 'Fam_class': 0.004382625269867411}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47582782550126645, 'Fam_class': -0.005212065845856755}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5207927180821353), 'Fam_class': np.float64(0.005054203690042603)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46772702388802034), 'Fam_class': np.float64(-0.005796360279022947)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.51804058717995), 'Fam_class': np.float64(0.004291942430938809)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46511008755203403), 'Fam_class': np.float64(-0.005094667171469625)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(26.836604996574742), 'Fam_class': np.float64(0.0018420769830492932)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.632739354266075), 'Fam_class': np.float64(0.0025955633588050308)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>1.842076983027408e-05</v>
+        <v>2.595563358787079e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.03941690323643662</v>
+        <v>0.06303157642181315</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8426511669015018</v>
+        <v>0.8017945188436659</v>
       </c>
     </row>
     <row r="4">
@@ -717,76 +717,76 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1546</v>
+        <v>1879</v>
       </c>
       <c r="E4" t="n">
-        <v>1541</v>
+        <v>1874</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2944199822974352</v>
+        <v>0.2480307255883233</v>
       </c>
       <c r="H4" t="n">
-        <v>160.7546916498718</v>
+        <v>154.5307752488205</v>
       </c>
       <c r="I4" t="n">
-        <v>4.597835696156709e-115</v>
+        <v>2.331306373584748e-114</v>
       </c>
       <c r="J4" t="n">
-        <v>168.4287048079192</v>
+        <v>205.0558981251997</v>
       </c>
       <c r="K4" t="n">
-        <v>238.7095730918499</v>
+        <v>272.691857370942</v>
       </c>
       <c r="L4" t="n">
-        <v>17.57021707098269</v>
+        <v>16.90898981143557</v>
       </c>
       <c r="M4" t="n">
-        <v>0.109298315903906</v>
+        <v>0.1094215038021343</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1545045780529773</v>
+        <v>0.145203331933409</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.6987180162877549, 'N1ratio-ArgsPreds': -0.1989128185427365, 'Fam_class': -0.00024353222093230985, 'Nlen_freq': -0.05335509829730006, 'Vlen_freq': 0.05730303379872109}</t>
+          <t>{'const': 0.5370618171394506, 'N1ratio-ArgsPreds': -2.128165518486883, 'Fam_class': -0.00036377344522275554, 'Nlen_freq': -0.5444306613549171, 'Vlen_freq': 0.8148346925701326}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 2.9358640081542937e-40, 'N1ratio-ArgsPreds': 3.3564045309057047e-100, 'Fam_class': 0.31974427031399666, 'Nlen_freq': 7.256439611194615e-06, 'Vlen_freq': 7.942901889449623e-09}</t>
+          <t>{'const': 2.2571253412342167e-63, 'N1ratio-ArgsPreds': 9.248568334714631e-97, 'Fam_class': 0.06200069385792821, 'Nlen_freq': 5.974684207527717e-07, 'Vlen_freq': 3.3128428934688257e-12}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5093489442763836, 'Fam_class': -0.022371527296775603, 'Nlen_freq': -0.17128957401764675, 'Vlen_freq': 0.22531296983375812}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4575914021867757, 'Fam_class': -0.03946288917812213, 'Nlen_freq': -0.18121886092509057, 'Vlen_freq': 0.2582527934088498}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5040373703975402), 'Fam_class': np.float64(-0.025346340159330728), 'Nlen_freq': np.float64(-0.11392364964468976), 'Vlen_freq': np.float64(0.14621020338354773)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4555266940908817), 'Fam_class': np.float64(-0.04309735592441534), 'Nlen_freq': np.float64(-0.11494973927851938), 'Vlen_freq': np.float64(0.1598501999515767)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4902099059378882), 'Fam_class': np.float64(-0.021297466495552423), 'Nlen_freq': np.float64(-0.09632161176336643), 'Vlen_freq': np.float64(0.12414899333501048)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4437266328482439), 'Fam_class': np.float64(-0.037407128773191335), 'Nlen_freq': np.float64(-0.10034515913759194), 'Vlen_freq': np.float64(0.14042159981875652)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(24.030575187963322), 'Fam_class': np.float64(0.0453582079129178), 'Nlen_freq': np.float64(0.9277852892692691), 'Vlen_freq': np.float64(1.5412972546096475)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.68933246988402), 'Fam_class': np.float64(0.1399293283054119), 'Nlen_freq': np.float64(1.0069150962348652), 'Vlen_freq': np.float64(1.9718225695658997)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.01551285145613446</v>
+        <v>0.02054462060800488</v>
       </c>
       <c r="V4" t="n">
-        <v>16.94017935183392</v>
+        <v>25.59986180919635</v>
       </c>
       <c r="W4" t="n">
-        <v>5.280596777667117e-08</v>
+        <v>1.074698771499114e-11</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_10_All_lg_families_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_10_All_lg_families_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2274601493467305</v>
+        <v>0.2216711997682284</v>
       </c>
       <c r="H2" t="n">
-        <v>552.6481254821807</v>
+        <v>534.5772144639448</v>
       </c>
       <c r="I2" t="n">
-        <v>2.509992414891764e-107</v>
+        <v>2.805806715175607e-104</v>
       </c>
       <c r="J2" t="n">
-        <v>210.6653267677102</v>
+        <v>210.7278626313512</v>
       </c>
       <c r="K2" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L2" t="n">
-        <v>62.02653060323181</v>
+        <v>60.01615014140037</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1122351234777358</v>
+        <v>0.1122684404002936</v>
       </c>
       <c r="N2" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5696950682749405, 'N1ratio-ArgsPreds': -2.2180953249680244}</t>
+          <t>{'const': 0.5567146824557327, 'N1ratio-ArgsPreds': -2.146484111162861}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 8.066049526466469e-170, 'N1ratio-ArgsPreds': 2.5099924148907162e-107}</t>
+          <t>{'const': 2.2155466928380838e-166, 'N1ratio-ArgsPreds': 2.8058067151748e-104}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4769278240433563}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4708197104712461}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47081971047124643)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4769278240433569)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4708197104712464)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.746014934673116)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.16711997682283)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2274861049803184</v>
+        <v>0.221736132632494</v>
       </c>
       <c r="H3" t="n">
-        <v>276.2176419701839</v>
+        <v>267.2467541282687</v>
       </c>
       <c r="I3" t="n">
-        <v>7.179746887012252e-106</v>
+        <v>7.53359073578489e-103</v>
       </c>
       <c r="J3" t="n">
-        <v>210.6582488777779</v>
+        <v>210.7102824471191</v>
       </c>
       <c r="K3" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L3" t="n">
-        <v>31.01680424658205</v>
+        <v>30.01686516281625</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1122911774401801</v>
+        <v>0.1123189138843918</v>
       </c>
       <c r="N3" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5714134856817259, 'N1ratio-ArgsPreds': -2.212979453130236, 'Fam_class': -4.804542163441746e-05}</t>
+          <t>{'const': 0.5594672996035288, 'N1ratio-ArgsPreds': -2.1387202477778535, 'Fam_class': -7.564945240760837e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.6803457582878222e-153, 'N1ratio-ArgsPreds': 1.0515195149464727e-102, 'Fam_class': 0.8017945188393122}</t>
+          <t>{'const': 5.379681521513522e-150, 'N1ratio-ArgsPreds': 1.0320607663038064e-99, 'Fam_class': 0.6924256437313685}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47582782550126645, 'Fam_class': -0.005212065845856755}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4691167489202811, 'Fam_class': -0.00823607566206608}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46772702388802034), 'Fam_class': np.float64(-0.005796360279022947)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4615418300813215), 'Fam_class': np.float64(-0.009133783850248652)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46511008755203403), 'Fam_class': np.float64(-0.005094667171469625)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4589790803977487), 'Fam_class': np.float64(-0.008058093091154971)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.632739354266075), 'Fam_class': np.float64(0.0025955633588050308)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.06617962427631), 'Fam_class': np.float64(0.006493286426571948)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>2.595563358787079e-05</v>
+        <v>6.493286426567657e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06303157642181315</v>
+        <v>0.1565202477849163</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8017945188436659</v>
+        <v>0.6924256437348864</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2480307255883233</v>
+        <v>0.2439809037842662</v>
       </c>
       <c r="H4" t="n">
-        <v>154.5307752488205</v>
+        <v>151.1933415373825</v>
       </c>
       <c r="I4" t="n">
-        <v>2.331306373584748e-114</v>
+        <v>3.517160776409304e-112</v>
       </c>
       <c r="J4" t="n">
-        <v>205.0558981251997</v>
+        <v>204.6876438422767</v>
       </c>
       <c r="K4" t="n">
-        <v>272.691857370942</v>
+        <v>270.7440127727515</v>
       </c>
       <c r="L4" t="n">
-        <v>16.90898981143557</v>
+        <v>16.51409223261871</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1094215038021343</v>
+        <v>0.1092249967141285</v>
       </c>
       <c r="N4" t="n">
-        <v>0.145203331933409</v>
+        <v>0.1441661409865557</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5370618171394506, 'N1ratio-ArgsPreds': -2.128165518486883, 'Fam_class': -0.00036377344522275554, 'Nlen_freq': -0.5444306613549171, 'Vlen_freq': 0.8148346925701326}</t>
+          <t>{'const': 0.5296445442831447, 'N1ratio-ArgsPreds': -2.0539984331631644, 'Fam_class': -0.00039554831215275635, 'Nlen_freq': -0.5803253406839579, 'Vlen_freq': 0.846947580572744}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 2.2571253412342167e-63, 'N1ratio-ArgsPreds': 9.248568334714631e-97, 'Fam_class': 0.06200069385792821, 'Nlen_freq': 5.974684207527717e-07, 'Vlen_freq': 3.3128428934688257e-12}</t>
+          <t>{'const': 4.59801617943541e-62, 'N1ratio-ArgsPreds': 7.338804432481835e-94, 'Fam_class': 0.04203921912987963, 'Nlen_freq': 9.193681948598536e-08, 'Vlen_freq': 3.64781750607151e-13}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4575914021867757, 'Fam_class': -0.03946288917812213, 'Nlen_freq': -0.18121886092509057, 'Vlen_freq': 0.2582527934088498}</t>
+          <t>{'N1ratio-ArgsPreds': -0.45053347592047455, 'Fam_class': -0.04306397102968304, 'Nlen_freq': -0.19407255926305564, 'Vlen_freq': 0.2697737447985525}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4555266940908817), 'Fam_class': np.float64(-0.04309735592441534), 'Nlen_freq': np.float64(-0.11494973927851938), 'Vlen_freq': np.float64(0.1598501999515767)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44927641391437984), 'Fam_class': np.float64(-0.0469460585096905), 'Nlen_freq': np.float64(-0.1229486188247275), 'Vlen_freq': np.float64(0.16673828182907574)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4437266328482439), 'Fam_class': np.float64(-0.037407128773191335), 'Nlen_freq': np.float64(-0.10034515913759194), 'Vlen_freq': np.float64(0.14042159981875652)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.43725778640066315), 'Fam_class': np.float64(-0.04086435273988635), 'Nlen_freq': np.float64(-0.10772030539472299), 'Vlen_freq': np.float64(0.1470361985062274)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.68933246988402), 'Fam_class': np.float64(0.1399293283054119), 'Nlen_freq': np.float64(1.0069150962348652), 'Vlen_freq': np.float64(1.9718225695658997)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.119437176800798), 'Fam_class': np.float64(0.16698953248498574), 'Nlen_freq': np.float64(1.1603664194332386), 'Vlen_freq': np.float64(2.161964367116271)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.02054462060800488</v>
+        <v>0.02224477115177215</v>
       </c>
       <c r="V4" t="n">
-        <v>25.59986180919635</v>
+        <v>27.5698731335521</v>
       </c>
       <c r="W4" t="n">
-        <v>1.074698771499114e-11</v>
+        <v>1.582435674219992e-12</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_10_All_lg_families_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_10_All_lg_families_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2216711997682284</v>
+        <v>0.2215000730459347</v>
       </c>
       <c r="H2" t="n">
-        <v>534.5772144639448</v>
+        <v>534.0471112616439</v>
       </c>
       <c r="I2" t="n">
-        <v>2.805806715175607e-104</v>
+        <v>3.450072936797282e-104</v>
       </c>
       <c r="J2" t="n">
-        <v>210.7278626313512</v>
+        <v>210.7741941668376</v>
       </c>
       <c r="K2" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L2" t="n">
-        <v>60.01615014140037</v>
+        <v>59.96981860591393</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1122684404002936</v>
+        <v>0.112293124223142</v>
       </c>
       <c r="N2" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5567146824557327, 'N1ratio-ArgsPreds': -2.146484111162861}</t>
+          <t>{'const': 0.5562505171853904, 'N1ratio-ArgsPreds': -2.142785220917257}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 2.2155466928380838e-166, 'N1ratio-ArgsPreds': 2.8058067151748e-104}</t>
+          <t>{'const': 2.611073940529163e-166, 'N1ratio-ArgsPreds': 3.45007293679726e-104}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4708197104712461}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47063794263311826}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47081971047124643)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47063794263311876)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4708197104712464)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47063794263311887)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.16711997682283)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.150007304593487)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.221736132632494</v>
+        <v>0.2215641810573831</v>
       </c>
       <c r="H3" t="n">
-        <v>267.2467541282687</v>
+        <v>266.9805227027272</v>
       </c>
       <c r="I3" t="n">
-        <v>7.53359073578489e-103</v>
+        <v>9.268235090907063e-103</v>
       </c>
       <c r="J3" t="n">
-        <v>210.7102824471191</v>
+        <v>210.7568373065672</v>
       </c>
       <c r="K3" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L3" t="n">
-        <v>30.01686516281625</v>
+        <v>29.99358773309218</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1123189138843918</v>
+        <v>0.1123437299075518</v>
       </c>
       <c r="N3" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5594672996035288, 'N1ratio-ArgsPreds': -2.1387202477778535, 'Fam_class': -7.564945240760837e-05}</t>
+          <t>{'const': 0.5589856011599725, 'N1ratio-ArgsPreds': -2.1350738576957373, 'Fam_class': -7.517046515621833e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 5.379681521513522e-150, 'N1ratio-ArgsPreds': 1.0320607663038064e-99, 'Fam_class': 0.6924256437313685}</t>
+          <t>{'const': 6.677300873815543e-150, 'N1ratio-ArgsPreds': 1.2702135053794654e-99, 'Fam_class': 0.6943182797021796}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4691167489202811, 'Fam_class': -0.00823607566206608}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46894423106275424, 'Fam_class': -0.008183927561609813}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4615418300813215), 'Fam_class': np.float64(-0.009133783850248652)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4613534260903031), 'Fam_class': np.float64(-0.009074586919709438)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4589790803977487), 'Fam_class': np.float64(-0.008058093091154971)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4587917225361234), 'Fam_class': np.float64(-0.008006747869677248)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.06617962427631), 'Fam_class': np.float64(0.006493286426571948)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.04898446676632), 'Fam_class': np.float64(0.006410801144858116)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>6.493286426567657e-05</v>
+        <v>6.410801144840494e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1565202477849163</v>
+        <v>0.1544978102890628</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6924256437348864</v>
+        <v>0.6943182797062395</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2439809037842662</v>
+        <v>0.243822021257772</v>
       </c>
       <c r="H4" t="n">
-        <v>151.1933415373825</v>
+        <v>151.0631361538313</v>
       </c>
       <c r="I4" t="n">
-        <v>3.517160776409304e-112</v>
+        <v>4.279780324521866e-112</v>
       </c>
       <c r="J4" t="n">
-        <v>204.6876438422767</v>
+        <v>204.7306603350592</v>
       </c>
       <c r="K4" t="n">
         <v>270.7440127727515</v>
       </c>
       <c r="L4" t="n">
-        <v>16.51409223261871</v>
+        <v>16.50333810942308</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1092249967141285</v>
+        <v>0.1092479510859441</v>
       </c>
       <c r="N4" t="n">
         <v>0.1441661409865557</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5296445442831447, 'N1ratio-ArgsPreds': -2.0539984331631644, 'Fam_class': -0.00039554831215275635, 'Nlen_freq': -0.5803253406839579, 'Vlen_freq': 0.846947580572744}</t>
+          <t>{'const': 0.5295592368727743, 'N1ratio-ArgsPreds': -2.0502685802895533, 'Fam_class': -0.00039472793058499534, 'Nlen_freq': -0.5894430598649993, 'Vlen_freq': 0.8476482717816196}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 4.59801617943541e-62, 'N1ratio-ArgsPreds': 7.338804432481835e-94, 'Fam_class': 0.04203921912987963, 'Nlen_freq': 9.193681948598536e-08, 'Vlen_freq': 3.64781750607151e-13}</t>
+          <t>{'const': 4.396456382516327e-62, 'N1ratio-ArgsPreds': 9.515116770681223e-94, 'Fam_class': 0.0424985905261426, 'Nlen_freq': 8.430248006269462e-08, 'Vlen_freq': 3.523337256418127e-13}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.45053347592047455, 'Fam_class': -0.04306397102968304, 'Nlen_freq': -0.19407255926305564, 'Vlen_freq': 0.2697737447985525}</t>
+          <t>{'N1ratio-ArgsPreds': -0.45031773462565816, 'Fam_class': -0.04297465478946179, 'Nlen_freq': -0.1947136848239577, 'Vlen_freq': 0.27004735426915216}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44927641391437984), 'Fam_class': np.float64(-0.0469460585096905), 'Nlen_freq': np.float64(-0.1229486188247275), 'Vlen_freq': np.float64(0.16673828182907574)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44903063138561533), 'Fam_class': np.float64(-0.04684163788303773), 'Nlen_freq': np.float64(-0.12330695649159294), 'Vlen_freq': np.float64(0.16684436452200357)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.43725778640066315), 'Fam_class': np.float64(-0.04086435273988635), 'Nlen_freq': np.float64(-0.10772030539472299), 'Vlen_freq': np.float64(0.1470361985062274)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4370040587381208), 'Fam_class': np.float64(-0.040777543526913484), 'Nlen_freq': np.float64(-0.10805045173376376), 'Vlen_freq': np.float64(0.1471478836936874)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.119437176800798), 'Fam_class': np.float64(0.16698953248498574), 'Nlen_freq': np.float64(1.1603664194332386), 'Vlen_freq': np.float64(2.161964367116271)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.097254735359094), 'Fam_class': np.float64(0.16628080560893238), 'Nlen_freq': np.float64(1.1674900119870413), 'Vlen_freq': np.float64(2.165249967553095)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.02224477115177215</v>
+        <v>0.0222578402003889</v>
       </c>
       <c r="V4" t="n">
-        <v>27.5698731335521</v>
+        <v>27.58027455712754</v>
       </c>
       <c r="W4" t="n">
-        <v>1.582435674219992e-12</v>
+        <v>1.566527139503497e-12</v>
       </c>
     </row>
   </sheetData>
